--- a/samples/fixtures/xlsx/multi-sheet.xlsx
+++ b/samples/fixtures/xlsx/multi-sheet.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,11 @@
           <t>Limit</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sprinklered</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -437,6 +442,116 @@
       </c>
       <c r="B2" t="n">
         <v>2000000</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>44 Quay Street</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7 Dockside</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9 Pier End</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alpha Wharf</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beta Dock</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gamma Yard</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Delta Port</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -450,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +579,11 @@
           <t>Amount</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -474,6 +594,11 @@
       <c r="B2" t="n">
         <v>6000</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -483,6 +608,56 @@
       </c>
       <c r="B3" t="n">
         <v>2000</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-01-22</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019-05-30</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>900</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
       </c>
     </row>
   </sheetData>
